--- a/score_data.xlsx
+++ b/score_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t713\Desktop\ScoreSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF4A234-399F-46FE-A01F-D08172D56B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB27A41-E204-4D07-955E-1640C0C93052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6921DC1A-4082-44FF-936E-F05E643CA0C8}"/>
   </bookViews>
@@ -679,36 +679,6 @@
       <c r="F2" s="1">
         <v>45</v>
       </c>
-      <c r="G2" s="1">
-        <v>45</v>
-      </c>
-      <c r="H2" s="1">
-        <v>78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>64</v>
-      </c>
-      <c r="J2" s="1">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1">
-        <v>33</v>
-      </c>
-      <c r="M2" s="1">
-        <v>59</v>
-      </c>
-      <c r="N2" s="1">
-        <v>44</v>
-      </c>
-      <c r="O2" s="1">
-        <v>65</v>
-      </c>
-      <c r="P2" s="1">
-        <v>93</v>
-      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
@@ -729,36 +699,6 @@
       <c r="F3" s="1">
         <v>334</v>
       </c>
-      <c r="G3" s="1">
-        <v>340</v>
-      </c>
-      <c r="H3" s="1">
-        <v>420</v>
-      </c>
-      <c r="I3" s="1">
-        <v>382</v>
-      </c>
-      <c r="J3" s="1">
-        <v>356</v>
-      </c>
-      <c r="K3" s="1">
-        <v>337</v>
-      </c>
-      <c r="L3" s="1">
-        <v>417</v>
-      </c>
-      <c r="M3" s="1">
-        <v>435</v>
-      </c>
-      <c r="N3" s="1">
-        <v>390</v>
-      </c>
-      <c r="O3" s="1">
-        <v>405</v>
-      </c>
-      <c r="P3" s="1">
-        <v>437</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
@@ -779,36 +719,6 @@
       <c r="F4" s="1">
         <v>276</v>
       </c>
-      <c r="G4" s="1">
-        <v>324</v>
-      </c>
-      <c r="H4" s="1">
-        <v>341</v>
-      </c>
-      <c r="I4" s="1">
-        <v>271</v>
-      </c>
-      <c r="J4" s="1">
-        <v>331</v>
-      </c>
-      <c r="K4" s="1">
-        <v>308</v>
-      </c>
-      <c r="L4" s="1">
-        <v>329</v>
-      </c>
-      <c r="M4" s="1">
-        <v>364</v>
-      </c>
-      <c r="N4" s="1">
-        <v>344</v>
-      </c>
-      <c r="O4" s="1">
-        <v>387</v>
-      </c>
-      <c r="P4" s="1">
-        <v>345</v>
-      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
@@ -829,36 +739,6 @@
       <c r="F5" s="1">
         <v>198</v>
       </c>
-      <c r="G5" s="1">
-        <v>117</v>
-      </c>
-      <c r="H5" s="1">
-        <v>148</v>
-      </c>
-      <c r="I5" s="1">
-        <v>56</v>
-      </c>
-      <c r="J5" s="1">
-        <v>138</v>
-      </c>
-      <c r="K5" s="1">
-        <v>127</v>
-      </c>
-      <c r="L5" s="1">
-        <v>135</v>
-      </c>
-      <c r="M5" s="1">
-        <v>64</v>
-      </c>
-      <c r="N5" s="1">
-        <v>55</v>
-      </c>
-      <c r="O5" s="1">
-        <v>115</v>
-      </c>
-      <c r="P5" s="1">
-        <v>177</v>
-      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
@@ -879,36 +759,6 @@
       <c r="F6" s="1">
         <v>150</v>
       </c>
-      <c r="G6" s="1">
-        <v>199</v>
-      </c>
-      <c r="H6" s="1">
-        <v>163</v>
-      </c>
-      <c r="I6" s="1">
-        <v>123</v>
-      </c>
-      <c r="J6" s="1">
-        <v>196</v>
-      </c>
-      <c r="K6" s="1">
-        <v>176</v>
-      </c>
-      <c r="L6" s="1">
-        <v>151</v>
-      </c>
-      <c r="M6" s="1">
-        <v>232</v>
-      </c>
-      <c r="N6" s="1">
-        <v>193</v>
-      </c>
-      <c r="O6" s="1">
-        <v>179</v>
-      </c>
-      <c r="P6" s="1">
-        <v>87</v>
-      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
@@ -929,36 +779,6 @@
       <c r="F7" s="1">
         <v>244</v>
       </c>
-      <c r="G7" s="1">
-        <v>169</v>
-      </c>
-      <c r="H7" s="1">
-        <v>305</v>
-      </c>
-      <c r="I7" s="1">
-        <v>250</v>
-      </c>
-      <c r="J7" s="1">
-        <v>161</v>
-      </c>
-      <c r="K7" s="1">
-        <v>222</v>
-      </c>
-      <c r="L7" s="1">
-        <v>201</v>
-      </c>
-      <c r="M7" s="1">
-        <v>257</v>
-      </c>
-      <c r="N7" s="1">
-        <v>170</v>
-      </c>
-      <c r="O7" s="1">
-        <v>203</v>
-      </c>
-      <c r="P7" s="1">
-        <v>208</v>
-      </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
@@ -979,36 +799,6 @@
       <c r="F8" s="1">
         <v>342</v>
       </c>
-      <c r="G8" s="1">
-        <v>286</v>
-      </c>
-      <c r="H8" s="1">
-        <v>324</v>
-      </c>
-      <c r="I8" s="1">
-        <v>284</v>
-      </c>
-      <c r="J8" s="1">
-        <v>258</v>
-      </c>
-      <c r="K8" s="1">
-        <v>347</v>
-      </c>
-      <c r="L8" s="1">
-        <v>334</v>
-      </c>
-      <c r="M8" s="1">
-        <v>390</v>
-      </c>
-      <c r="N8" s="1">
-        <v>318</v>
-      </c>
-      <c r="O8" s="1">
-        <v>301</v>
-      </c>
-      <c r="P8" s="1">
-        <v>362</v>
-      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
@@ -1029,36 +819,6 @@
       <c r="F9" s="1">
         <v>249</v>
       </c>
-      <c r="G9" s="1">
-        <v>284</v>
-      </c>
-      <c r="H9" s="1">
-        <v>228</v>
-      </c>
-      <c r="I9" s="1">
-        <v>221</v>
-      </c>
-      <c r="J9" s="1">
-        <v>321</v>
-      </c>
-      <c r="K9" s="1">
-        <v>286</v>
-      </c>
-      <c r="L9" s="1">
-        <v>359</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>280</v>
-      </c>
-      <c r="O9" s="1">
-        <v>263</v>
-      </c>
-      <c r="P9" s="1">
-        <v>234</v>
-      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
@@ -1079,36 +839,6 @@
       <c r="F10" s="1">
         <v>392</v>
       </c>
-      <c r="G10" s="1">
-        <v>512</v>
-      </c>
-      <c r="H10" s="1">
-        <v>423</v>
-      </c>
-      <c r="I10" s="1">
-        <v>464</v>
-      </c>
-      <c r="J10" s="1">
-        <v>415</v>
-      </c>
-      <c r="K10" s="1">
-        <v>445</v>
-      </c>
-      <c r="L10" s="1">
-        <v>402</v>
-      </c>
-      <c r="M10" s="1">
-        <v>424</v>
-      </c>
-      <c r="N10" s="1">
-        <v>476</v>
-      </c>
-      <c r="O10" s="1">
-        <v>496</v>
-      </c>
-      <c r="P10" s="1">
-        <v>438</v>
-      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
@@ -1129,36 +859,6 @@
       <c r="F11" s="1">
         <v>351</v>
       </c>
-      <c r="G11" s="1">
-        <v>343</v>
-      </c>
-      <c r="H11" s="1">
-        <v>146</v>
-      </c>
-      <c r="I11" s="1">
-        <v>225</v>
-      </c>
-      <c r="J11" s="1">
-        <v>196</v>
-      </c>
-      <c r="K11" s="1">
-        <v>264</v>
-      </c>
-      <c r="L11" s="1">
-        <v>279</v>
-      </c>
-      <c r="M11" s="1">
-        <v>270</v>
-      </c>
-      <c r="N11" s="1">
-        <v>356</v>
-      </c>
-      <c r="O11" s="1">
-        <v>303</v>
-      </c>
-      <c r="P11" s="1">
-        <v>317</v>
-      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
@@ -1179,36 +879,6 @@
       <c r="F12" s="1">
         <v>269</v>
       </c>
-      <c r="G12" s="1">
-        <v>225</v>
-      </c>
-      <c r="H12" s="1">
-        <v>225</v>
-      </c>
-      <c r="I12" s="1">
-        <v>256</v>
-      </c>
-      <c r="J12" s="1">
-        <v>220</v>
-      </c>
-      <c r="K12" s="1">
-        <v>167</v>
-      </c>
-      <c r="L12" s="1">
-        <v>173</v>
-      </c>
-      <c r="M12" s="1">
-        <v>246</v>
-      </c>
-      <c r="N12" s="1">
-        <v>242</v>
-      </c>
-      <c r="O12" s="1">
-        <v>184</v>
-      </c>
-      <c r="P12" s="1">
-        <v>173</v>
-      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
@@ -1229,36 +899,6 @@
       <c r="F13" s="1">
         <v>18</v>
       </c>
-      <c r="G13" s="1">
-        <v>29</v>
-      </c>
-      <c r="H13" s="1">
-        <v>60</v>
-      </c>
-      <c r="I13" s="1">
-        <v>25</v>
-      </c>
-      <c r="J13" s="1">
-        <v>21</v>
-      </c>
-      <c r="K13" s="1">
-        <v>12</v>
-      </c>
-      <c r="L13" s="1">
-        <v>33</v>
-      </c>
-      <c r="M13" s="1">
-        <v>26</v>
-      </c>
-      <c r="N13" s="1">
-        <v>41</v>
-      </c>
-      <c r="O13" s="1">
-        <v>48</v>
-      </c>
-      <c r="P13" s="1">
-        <v>58</v>
-      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
@@ -1279,36 +919,6 @@
       <c r="F14" s="1">
         <v>244</v>
       </c>
-      <c r="G14" s="1">
-        <v>230</v>
-      </c>
-      <c r="H14" s="1">
-        <v>222</v>
-      </c>
-      <c r="I14" s="1">
-        <v>272</v>
-      </c>
-      <c r="J14" s="1">
-        <v>212</v>
-      </c>
-      <c r="K14" s="1">
-        <v>219</v>
-      </c>
-      <c r="L14" s="1">
-        <v>176</v>
-      </c>
-      <c r="M14" s="1">
-        <v>256</v>
-      </c>
-      <c r="N14" s="1">
-        <v>253</v>
-      </c>
-      <c r="O14" s="1">
-        <v>218</v>
-      </c>
-      <c r="P14" s="1">
-        <v>190</v>
-      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
@@ -1329,36 +939,6 @@
       <c r="F15" s="1">
         <v>425</v>
       </c>
-      <c r="G15" s="1">
-        <v>469</v>
-      </c>
-      <c r="H15" s="1">
-        <v>491</v>
-      </c>
-      <c r="I15" s="1">
-        <v>451</v>
-      </c>
-      <c r="J15" s="1">
-        <v>469</v>
-      </c>
-      <c r="K15" s="1">
-        <v>510</v>
-      </c>
-      <c r="L15" s="1">
-        <v>504</v>
-      </c>
-      <c r="M15" s="1">
-        <v>529</v>
-      </c>
-      <c r="N15" s="1">
-        <v>537</v>
-      </c>
-      <c r="O15" s="1">
-        <v>545</v>
-      </c>
-      <c r="P15" s="1">
-        <v>527</v>
-      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
@@ -1379,35 +959,8 @@
       <c r="F16" s="1">
         <v>0</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>24</v>
       </c>
@@ -1426,38 +979,8 @@
       <c r="F17" s="1">
         <v>515</v>
       </c>
-      <c r="G17" s="1">
-        <v>490</v>
-      </c>
-      <c r="H17" s="1">
-        <v>521</v>
-      </c>
-      <c r="I17" s="1">
-        <v>554</v>
-      </c>
-      <c r="J17" s="1">
-        <v>534</v>
-      </c>
-      <c r="K17" s="1">
-        <v>455</v>
-      </c>
-      <c r="L17" s="1">
-        <v>504</v>
-      </c>
-      <c r="M17" s="1">
-        <v>504</v>
-      </c>
-      <c r="N17" s="1">
-        <v>508</v>
-      </c>
-      <c r="O17" s="1">
-        <v>535</v>
-      </c>
-      <c r="P17" s="1">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>25</v>
       </c>
@@ -1476,38 +999,8 @@
       <c r="F18" s="1">
         <v>250</v>
       </c>
-      <c r="G18" s="1">
-        <v>187</v>
-      </c>
-      <c r="H18" s="1">
-        <v>181</v>
-      </c>
-      <c r="I18" s="1">
-        <v>225</v>
-      </c>
-      <c r="J18" s="1">
-        <v>362</v>
-      </c>
-      <c r="K18" s="1">
-        <v>281</v>
-      </c>
-      <c r="L18" s="1">
-        <v>336</v>
-      </c>
-      <c r="M18" s="1">
-        <v>330</v>
-      </c>
-      <c r="N18" s="1">
-        <v>440</v>
-      </c>
-      <c r="O18" s="1">
-        <v>432</v>
-      </c>
-      <c r="P18" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -1526,38 +1019,8 @@
       <c r="F19" s="1">
         <v>259</v>
       </c>
-      <c r="G19" s="1">
-        <v>326</v>
-      </c>
-      <c r="H19" s="1">
-        <v>224</v>
-      </c>
-      <c r="I19" s="1">
-        <v>372</v>
-      </c>
-      <c r="J19" s="1">
-        <v>392</v>
-      </c>
-      <c r="K19" s="1">
-        <v>382</v>
-      </c>
-      <c r="L19" s="1">
-        <v>435</v>
-      </c>
-      <c r="M19" s="1">
-        <v>454</v>
-      </c>
-      <c r="N19" s="1">
-        <v>461</v>
-      </c>
-      <c r="O19" s="1">
-        <v>323</v>
-      </c>
-      <c r="P19" s="1">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>27</v>
       </c>
@@ -1576,38 +1039,8 @@
       <c r="F20" s="1">
         <v>458</v>
       </c>
-      <c r="G20" s="1">
-        <v>506</v>
-      </c>
-      <c r="H20" s="1">
-        <v>448</v>
-      </c>
-      <c r="I20" s="1">
-        <v>466</v>
-      </c>
-      <c r="J20" s="1">
-        <v>473</v>
-      </c>
-      <c r="K20" s="1">
-        <v>453</v>
-      </c>
-      <c r="L20" s="1">
-        <v>433</v>
-      </c>
-      <c r="M20" s="1">
-        <v>475</v>
-      </c>
-      <c r="N20" s="1">
-        <v>503</v>
-      </c>
-      <c r="O20" s="1">
-        <v>521</v>
-      </c>
-      <c r="P20" s="1">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>28</v>
       </c>
@@ -1626,38 +1059,8 @@
       <c r="F21" s="1">
         <v>359</v>
       </c>
-      <c r="G21" s="1">
-        <v>289</v>
-      </c>
-      <c r="H21" s="1">
-        <v>319</v>
-      </c>
-      <c r="I21" s="1">
-        <v>342</v>
-      </c>
-      <c r="J21" s="1">
-        <v>289</v>
-      </c>
-      <c r="K21" s="1">
-        <v>266</v>
-      </c>
-      <c r="L21" s="1">
-        <v>197</v>
-      </c>
-      <c r="M21" s="1">
-        <v>220</v>
-      </c>
-      <c r="N21" s="1">
-        <v>208</v>
-      </c>
-      <c r="O21" s="1">
-        <v>234</v>
-      </c>
-      <c r="P21" s="1">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>29</v>
       </c>
@@ -1676,38 +1079,8 @@
       <c r="F22" s="1">
         <v>35</v>
       </c>
-      <c r="G22" s="1">
-        <v>71</v>
-      </c>
-      <c r="H22" s="1">
-        <v>135</v>
-      </c>
-      <c r="I22" s="1">
-        <v>70</v>
-      </c>
-      <c r="J22" s="1">
-        <v>40</v>
-      </c>
-      <c r="K22" s="1">
-        <v>56</v>
-      </c>
-      <c r="L22" s="1">
-        <v>71</v>
-      </c>
-      <c r="M22" s="1">
-        <v>112</v>
-      </c>
-      <c r="N22" s="1">
-        <v>51</v>
-      </c>
-      <c r="O22" s="1">
-        <v>32</v>
-      </c>
-      <c r="P22" s="1">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>30</v>
       </c>
@@ -1726,38 +1099,8 @@
       <c r="F23" s="1">
         <v>257</v>
       </c>
-      <c r="G23" s="1">
-        <v>218</v>
-      </c>
-      <c r="H23" s="1">
-        <v>291</v>
-      </c>
-      <c r="I23" s="1">
-        <v>225</v>
-      </c>
-      <c r="J23" s="1">
-        <v>220</v>
-      </c>
-      <c r="K23" s="1">
-        <v>146</v>
-      </c>
-      <c r="L23" s="1">
-        <v>210</v>
-      </c>
-      <c r="M23" s="1">
-        <v>302</v>
-      </c>
-      <c r="N23" s="1">
-        <v>161</v>
-      </c>
-      <c r="O23" s="1">
-        <v>252</v>
-      </c>
-      <c r="P23" s="1">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>31</v>
       </c>
@@ -1776,38 +1119,8 @@
       <c r="F24" s="1">
         <v>536</v>
       </c>
-      <c r="G24" s="1">
-        <v>501</v>
-      </c>
-      <c r="H24" s="1">
-        <v>520</v>
-      </c>
-      <c r="I24" s="1">
-        <v>517</v>
-      </c>
-      <c r="J24" s="1">
-        <v>536</v>
-      </c>
-      <c r="K24" s="1">
-        <v>540</v>
-      </c>
-      <c r="L24" s="1">
-        <v>527</v>
-      </c>
-      <c r="M24" s="1">
-        <v>520</v>
-      </c>
-      <c r="N24" s="1">
-        <v>511</v>
-      </c>
-      <c r="O24" s="1">
-        <v>531</v>
-      </c>
-      <c r="P24" s="1">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>32</v>
       </c>
@@ -1826,38 +1139,8 @@
       <c r="F25" s="1">
         <v>86</v>
       </c>
-      <c r="G25" s="1">
-        <v>85</v>
-      </c>
-      <c r="H25" s="1">
-        <v>30</v>
-      </c>
-      <c r="I25" s="1">
-        <v>51</v>
-      </c>
-      <c r="J25" s="1">
-        <v>41</v>
-      </c>
-      <c r="K25" s="1">
-        <v>71</v>
-      </c>
-      <c r="L25" s="1">
-        <v>64</v>
-      </c>
-      <c r="M25" s="1">
-        <v>141</v>
-      </c>
-      <c r="N25" s="1">
-        <v>63</v>
-      </c>
-      <c r="O25" s="1">
-        <v>84</v>
-      </c>
-      <c r="P25" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>33</v>
       </c>
@@ -1876,38 +1159,8 @@
       <c r="F26" s="1">
         <v>375</v>
       </c>
-      <c r="G26" s="1">
-        <v>443</v>
-      </c>
-      <c r="H26" s="1">
-        <v>381</v>
-      </c>
-      <c r="I26" s="1">
-        <v>424</v>
-      </c>
-      <c r="J26" s="1">
-        <v>377</v>
-      </c>
-      <c r="K26" s="1">
-        <v>396</v>
-      </c>
-      <c r="L26" s="1">
-        <v>366</v>
-      </c>
-      <c r="M26" s="1">
-        <v>441</v>
-      </c>
-      <c r="N26" s="1">
-        <v>396</v>
-      </c>
-      <c r="O26" s="1">
-        <v>452</v>
-      </c>
-      <c r="P26" s="1">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>34</v>
       </c>
@@ -1926,38 +1179,8 @@
       <c r="F27" s="1">
         <v>46</v>
       </c>
-      <c r="G27" s="1">
-        <v>58</v>
-      </c>
-      <c r="H27" s="1">
-        <v>86</v>
-      </c>
-      <c r="I27" s="1">
-        <v>162</v>
-      </c>
-      <c r="J27" s="1">
-        <v>11</v>
-      </c>
-      <c r="K27" s="1">
-        <v>138</v>
-      </c>
-      <c r="L27" s="1">
-        <v>161</v>
-      </c>
-      <c r="M27" s="1">
-        <v>88</v>
-      </c>
-      <c r="N27" s="1">
-        <v>113</v>
-      </c>
-      <c r="O27" s="1">
-        <v>71</v>
-      </c>
-      <c r="P27" s="1">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>35</v>
       </c>
@@ -1976,38 +1199,8 @@
       <c r="F28" s="1">
         <v>315</v>
       </c>
-      <c r="G28" s="1">
-        <v>234</v>
-      </c>
-      <c r="H28" s="1">
-        <v>267</v>
-      </c>
-      <c r="I28" s="1">
-        <v>363</v>
-      </c>
-      <c r="J28" s="1">
-        <v>300</v>
-      </c>
-      <c r="K28" s="1">
-        <v>256</v>
-      </c>
-      <c r="L28" s="1">
-        <v>261</v>
-      </c>
-      <c r="M28" s="1">
-        <v>246</v>
-      </c>
-      <c r="N28" s="1">
-        <v>232</v>
-      </c>
-      <c r="O28" s="1">
-        <v>293</v>
-      </c>
-      <c r="P28" s="1">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>36</v>
       </c>
@@ -2025,36 +1218,6 @@
       </c>
       <c r="F29" s="1">
         <v>74</v>
-      </c>
-      <c r="G29" s="1">
-        <v>77</v>
-      </c>
-      <c r="H29" s="1">
-        <v>50</v>
-      </c>
-      <c r="I29" s="1">
-        <v>63</v>
-      </c>
-      <c r="J29" s="1">
-        <v>32</v>
-      </c>
-      <c r="K29" s="1">
-        <v>82</v>
-      </c>
-      <c r="L29" s="1">
-        <v>78</v>
-      </c>
-      <c r="M29" s="1">
-        <v>78</v>
-      </c>
-      <c r="N29" s="1">
-        <v>27</v>
-      </c>
-      <c r="O29" s="1">
-        <v>152</v>
-      </c>
-      <c r="P29" s="1">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
